--- a/SGC-CKN/Excel/042b8999-8062-40f1-9435-db64c31f4ecf_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-3_D800_08-03-2026.xlsx
+++ b/SGC-CKN/Excel/042b8999-8062-40f1-9435-db64c31f4ecf_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-3_D800_08-03-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P7-3</t>
+    <t>P7-03</t>
   </si>
   <si>
     <t>Biên bản số</t>
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
+    <t>Sét xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">19h03
@@ -166,7 +166,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10h10
@@ -180,7 +180,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">13h00
@@ -192,9 +192,6 @@
   </si>
   <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">13h41
@@ -1494,13 +1491,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>57</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>58</v>
       </c>
       <c r="F19" s="31">
         <v>-38.7</v>
@@ -1523,19 +1520,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>61</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>62</v>
       </c>
       <c r="F20" s="34">
         <v>-44.45</v>
@@ -1558,7 +1555,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1664,31 +1661,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1931,7 +1928,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1960,7 +1957,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -1983,7 +1980,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>

--- a/SGC-CKN/Excel/042b8999-8062-40f1-9435-db64c31f4ecf_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-3_D800_08-03-2026.xlsx
+++ b/SGC-CKN/Excel/042b8999-8062-40f1-9435-db64c31f4ecf_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-3_D800_08-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
   <si>
     <t>Dự án</t>
   </si>
@@ -38,10 +38,10 @@
     <t>P7-03</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>KCL-0001</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">17h00
@@ -106,13 +106,10 @@
 07/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">17h58
@@ -122,9 +119,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh TT dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">19h03
 07/03/2026</t>
   </si>
@@ -146,7 +140,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08h40
@@ -156,9 +150,6 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">09h45
 08/03/2026</t>
   </si>
@@ -166,7 +157,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">10h10
@@ -180,7 +171,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">13h00
@@ -205,7 +196,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, TT chặt đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15h16
@@ -250,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -326,11 +317,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -343,7 +329,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -418,11 +404,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -518,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -619,22 +600,13 @@
     <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1235,24 +1207,24 @@
         <v>4.71</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F12" s="9">
         <v>-7.4</v>
@@ -1270,24 +1242,24 @@
         <v>12.55</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F13" s="13">
         <v>-9.7</v>
@@ -1305,24 +1277,24 @@
         <v>7.57</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>38</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="16">
         <v>-17.9</v>
@@ -1340,24 +1312,24 @@
         <v>8.7</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F15" s="19">
         <v>-22.25</v>
@@ -1375,198 +1347,198 @@
         <v>3.69</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="22" t="s">
+      <c r="A16" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="24" t="s">
+      <c r="C16" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="F16" s="19">
         <v>-26.25</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="19">
         <v>-34.5</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="19">
         <v>1.08</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="19">
         <v>8.25</v>
       </c>
       <c r="J16" s="12">
         <v>7.62</v>
       </c>
-      <c r="K16" s="23" t="s">
-        <v>30</v>
+      <c r="K16" s="20" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="22">
         <v>-34.5</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="22">
         <v>-37.1</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="22">
         <v>1.7</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="22">
         <v>2.6</v>
       </c>
       <c r="J17" s="8">
         <v>1.53</v>
       </c>
-      <c r="K17" s="26" t="s">
-        <v>30</v>
+      <c r="K17" s="23" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="25">
         <v>-37.1</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="25">
         <v>-38.7</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="25">
         <v>0.67</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="25">
         <v>1.6</v>
       </c>
       <c r="J18" s="8">
         <v>2.4</v>
       </c>
-      <c r="K18" s="29" t="s">
-        <v>30</v>
+      <c r="K18" s="26" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="31" t="s">
+      <c r="A19" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="31">
+      <c r="C19" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="28">
         <v>-38.7</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="28">
         <v>-44.45</v>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="28">
         <v>1.57</v>
       </c>
-      <c r="I19" s="31">
+      <c r="I19" s="28">
         <v>5.75</v>
       </c>
       <c r="J19" s="8">
         <v>3.67</v>
       </c>
-      <c r="K19" s="32" t="s">
-        <v>30</v>
+      <c r="K19" s="29" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
+      <c r="A20" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="34">
+      <c r="F20" s="31">
         <v>-44.45</v>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="31">
         <v>-45.1</v>
       </c>
-      <c r="H20" s="34">
+      <c r="H20" s="31">
         <v>0.48</v>
       </c>
-      <c r="I20" s="34">
+      <c r="I20" s="31">
         <v>0.65</v>
       </c>
       <c r="J20" s="8">
         <v>1.34</v>
       </c>
-      <c r="K20" s="35" t="s">
-        <v>30</v>
+      <c r="K20" s="32" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
+      <c r="A23" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1648,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1661,31 +1633,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1725,7 +1697,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1754,7 +1726,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1783,7 +1755,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1812,25 +1784,25 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D6" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="19">
         <v>-22.25</v>
       </c>
       <c r="F6" s="19">
-        <v>-26.25</v>
+        <v>-34.5</v>
       </c>
       <c r="G6" s="19">
-        <v>1.08</v>
+        <v>2.17</v>
       </c>
       <c r="H6" s="19">
-        <v>4</v>
-      </c>
-      <c r="I6" s="8">
-        <v>3.69</v>
+        <v>12.25</v>
+      </c>
+      <c r="I6" s="12">
+        <v>5.65</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1847,19 +1819,19 @@
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>-26.25</v>
+        <v>-34.5</v>
       </c>
       <c r="F7" s="22">
-        <v>-34.5</v>
+        <v>-37.1</v>
       </c>
       <c r="G7" s="22">
-        <v>1.08</v>
+        <v>1.7</v>
       </c>
       <c r="H7" s="22">
-        <v>8.25</v>
-      </c>
-      <c r="I7" s="12">
-        <v>7.62</v>
+        <v>2.6</v>
+      </c>
+      <c r="I7" s="8">
+        <v>1.53</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1870,25 +1842,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-34.5</v>
+        <v>-37.1</v>
       </c>
       <c r="F8" s="25">
-        <v>-37.1</v>
+        <v>-38.7</v>
       </c>
       <c r="G8" s="25">
-        <v>1.7</v>
+        <v>0.67</v>
       </c>
       <c r="H8" s="25">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="I8" s="8">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1899,25 +1871,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>-37.1</v>
+        <v>-38.7</v>
       </c>
       <c r="F9" s="28">
-        <v>-38.7</v>
+        <v>-44.45</v>
       </c>
       <c r="G9" s="28">
-        <v>0.67</v>
+        <v>1.57</v>
       </c>
       <c r="H9" s="28">
-        <v>1.6</v>
+        <v>5.75</v>
       </c>
       <c r="I9" s="8">
-        <v>2.4</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1928,82 +1900,53 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>-38.7</v>
+        <v>-44.45</v>
       </c>
       <c r="F10" s="31">
-        <v>-44.45</v>
+        <v>-45.1</v>
       </c>
       <c r="G10" s="31">
-        <v>1.57</v>
+        <v>0.48</v>
       </c>
       <c r="H10" s="31">
-        <v>5.75</v>
+        <v>0.65</v>
       </c>
       <c r="I10" s="8">
-        <v>3.67</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="36">
         <v>10</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-44.45</v>
-      </c>
-      <c r="F11" s="34">
+      <c r="E11" s="36">
+        <v>-3.71</v>
+      </c>
+      <c r="F11" s="36">
         <v>-45.1</v>
       </c>
-      <c r="G11" s="34">
-        <v>0.48</v>
-      </c>
-      <c r="H11" s="34">
-        <v>0.65</v>
-      </c>
-      <c r="I11" s="8">
-        <v>1.34</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="39">
-        <v>10</v>
-      </c>
-      <c r="E12" s="39">
-        <v>-3.71</v>
-      </c>
-      <c r="F12" s="39">
-        <v>-45.1</v>
-      </c>
-      <c r="G12" s="39">
+      <c r="G11" s="36">
         <v>9.13</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H11" s="36">
         <v>41.39</v>
       </c>
-      <c r="I12" s="39">
+      <c r="I11" s="36">
         <v>4.53</v>
       </c>
     </row>

--- a/SGC-CKN/Excel/042b8999-8062-40f1-9435-db64c31f4ecf_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-3_D800_08-03-2026.xlsx
+++ b/SGC-CKN/Excel/042b8999-8062-40f1-9435-db64c31f4ecf_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-3_D800_08-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="70">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGC-KCN0001</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -104,6 +104,9 @@
   <si>
     <t xml:space="preserve">17h47
 07/03/2026</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>2</t>
@@ -1207,24 +1210,24 @@
         <v>4.71</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F12" s="9">
         <v>-7.4</v>
@@ -1242,12 +1245,12 @@
         <v>12.55</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
@@ -1256,10 +1259,10 @@
         <v>27</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F13" s="13">
         <v>-9.7</v>
@@ -1277,24 +1280,24 @@
         <v>7.57</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="16">
         <v>-17.9</v>
@@ -1312,24 +1315,24 @@
         <v>8.7</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="19">
         <v>-22.25</v>
@@ -1347,24 +1350,24 @@
         <v>3.69</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" s="19">
         <v>-26.25</v>
@@ -1382,24 +1385,24 @@
         <v>7.62</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="22">
         <v>-34.5</v>
@@ -1417,24 +1420,24 @@
         <v>1.53</v>
       </c>
       <c r="K17" s="23" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" s="25">
         <v>-37.1</v>
@@ -1452,24 +1455,24 @@
         <v>2.4</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="28">
         <v>-38.7</v>
@@ -1487,24 +1490,24 @@
         <v>3.67</v>
       </c>
       <c r="K19" s="29" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F20" s="31">
         <v>-44.45</v>
@@ -1522,12 +1525,12 @@
         <v>1.34</v>
       </c>
       <c r="K20" s="32" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -1633,31 +1636,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1697,7 +1700,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1755,7 +1758,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1784,7 +1787,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19">
         <v>2</v>
@@ -1813,7 +1816,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1842,7 +1845,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1871,7 +1874,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1900,7 +1903,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1923,13 +1926,13 @@
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D11" s="36">
         <v>10</v>

--- a/SGC-CKN/Excel/042b8999-8062-40f1-9435-db64c31f4ecf_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-3_D800_08-03-2026.xlsx
+++ b/SGC-CKN/Excel/042b8999-8062-40f1-9435-db64c31f4ecf_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P7-3_D800_08-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="71">
   <si>
     <t>Dự án</t>
   </si>
@@ -23,7 +23,7 @@
     <t>Hạng mục</t>
   </si>
   <si>
-    <t>Thi công cọc khoan nhồi đại trà_lô đất ký hiệu CT-02</t>
+    <t>Thi công cọc khoan nhồi, tường vây cho các hạng mục_Lô CT-02</t>
   </si>
   <si>
     <t>Tên bộ phận</t>
@@ -102,7 +102,7 @@
 07/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">17h47
+    <t xml:space="preserve">17h17
 07/03/2026</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">17h58
+    <t xml:space="preserve">17h25
 07/03/2026</t>
   </si>
   <si>
@@ -144,6 +144,10 @@
   </si>
   <si>
     <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07h36
+08/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">08h40
@@ -361,17 +365,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
+        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFDE68A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1FAE5"/>
       </patternFill>
     </fill>
     <fill>
@@ -387,6 +386,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -537,35 +541,35 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1201,13 +1205,13 @@
         <v>-7.4</v>
       </c>
       <c r="H11" s="5">
-        <v>0.78</v>
+        <v>0.28</v>
       </c>
       <c r="I11" s="5">
         <v>3.69</v>
       </c>
       <c r="J11" s="8">
-        <v>4.71</v>
+        <v>13.02</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1236,173 +1240,173 @@
         <v>-9.7</v>
       </c>
       <c r="H12" s="9">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="I12" s="9">
         <v>2.3</v>
       </c>
-      <c r="J12" s="12">
-        <v>12.55</v>
+      <c r="J12" s="8">
+        <v>17.25</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>-9.7</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <v>-17.9</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
+        <v>1.63</v>
+      </c>
+      <c r="I13" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="J13" s="8">
+        <v>5.02</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="15">
+        <v>-17.9</v>
+      </c>
+      <c r="G14" s="15">
+        <v>-22.25</v>
+      </c>
+      <c r="H14" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="I14" s="15">
+        <v>4.35</v>
+      </c>
+      <c r="J14" s="8">
+        <v>8.7</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="18">
+        <v>-22.25</v>
+      </c>
+      <c r="G15" s="18">
+        <v>-26.25</v>
+      </c>
+      <c r="H15" s="18">
+        <v>1.07</v>
+      </c>
+      <c r="I15" s="18">
+        <v>4</v>
+      </c>
+      <c r="J15" s="21">
+        <v>3.75</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="18">
+        <v>-26.25</v>
+      </c>
+      <c r="G16" s="18">
+        <v>-34.5</v>
+      </c>
+      <c r="H16" s="18">
         <v>1.08</v>
       </c>
-      <c r="I13" s="13">
-        <v>8.2</v>
-      </c>
-      <c r="J13" s="12">
-        <v>7.57</v>
-      </c>
-      <c r="K13" s="14" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="16">
-        <v>-17.9</v>
-      </c>
-      <c r="G14" s="16">
-        <v>-22.25</v>
-      </c>
-      <c r="H14" s="16">
-        <v>0.5</v>
-      </c>
-      <c r="I14" s="16">
-        <v>4.35</v>
-      </c>
-      <c r="J14" s="12">
-        <v>8.7</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="19">
-        <v>-22.25</v>
-      </c>
-      <c r="G15" s="19">
-        <v>-26.25</v>
-      </c>
-      <c r="H15" s="19">
-        <v>1.08</v>
-      </c>
-      <c r="I15" s="19">
-        <v>4</v>
-      </c>
-      <c r="J15" s="8">
-        <v>3.69</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E16" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="19">
-        <v>-26.25</v>
-      </c>
-      <c r="G16" s="19">
-        <v>-34.5</v>
-      </c>
-      <c r="H16" s="19">
-        <v>1.08</v>
-      </c>
-      <c r="I16" s="19">
+      <c r="I16" s="18">
         <v>8.25</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="8">
         <v>7.62</v>
       </c>
-      <c r="K16" s="20" t="s">
+      <c r="K16" s="19" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="22">
         <v>-34.5</v>
@@ -1416,7 +1420,7 @@
       <c r="I17" s="22">
         <v>2.6</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="21">
         <v>1.53</v>
       </c>
       <c r="K17" s="23" t="s">
@@ -1425,19 +1429,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="25">
         <v>-37.1</v>
@@ -1451,7 +1455,7 @@
       <c r="I18" s="25">
         <v>1.6</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="21">
         <v>2.4</v>
       </c>
       <c r="K18" s="26" t="s">
@@ -1460,19 +1464,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D19" s="30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E19" s="30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F19" s="28">
         <v>-38.7</v>
@@ -1486,7 +1490,7 @@
       <c r="I19" s="28">
         <v>5.75</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="21">
         <v>3.67</v>
       </c>
       <c r="K19" s="29" t="s">
@@ -1495,19 +1499,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="31">
         <v>-44.45</v>
@@ -1521,7 +1525,7 @@
       <c r="I20" s="31">
         <v>0.65</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="21">
         <v>1.34</v>
       </c>
       <c r="K20" s="32" t="s">
@@ -1530,7 +1534,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B23" s="34"/>
       <c r="C23" s="34"/>
@@ -1636,31 +1640,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1683,13 +1687,13 @@
         <v>-7.4</v>
       </c>
       <c r="G2" s="5">
-        <v>0.78</v>
+        <v>0.28</v>
       </c>
       <c r="H2" s="5">
         <v>3.69</v>
       </c>
       <c r="I2" s="8">
-        <v>4.71</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1712,100 +1716,100 @@
         <v>-9.7</v>
       </c>
       <c r="G3" s="9">
-        <v>0.18</v>
+        <v>0.13</v>
       </c>
       <c r="H3" s="9">
         <v>2.3</v>
       </c>
-      <c r="I3" s="12">
-        <v>12.55</v>
+      <c r="I3" s="8">
+        <v>17.25</v>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>-9.7</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>-17.9</v>
       </c>
-      <c r="G4" s="13">
-        <v>1.08</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="G4" s="12">
+        <v>1.63</v>
+      </c>
+      <c r="H4" s="12">
         <v>8.2</v>
       </c>
-      <c r="I4" s="12">
-        <v>7.57</v>
+      <c r="I4" s="8">
+        <v>5.02</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
+      <c r="A5" s="15">
         <v>4</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="16">
+      <c r="D5" s="15">
         <v>1</v>
       </c>
-      <c r="E5" s="16">
+      <c r="E5" s="15">
         <v>-17.9</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="15">
         <v>-22.25</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="15">
         <v>0.5</v>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="15">
         <v>4.35</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="8">
         <v>8.7</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="18">
         <v>2</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="18">
         <v>-22.25</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="18">
         <v>-34.5</v>
       </c>
-      <c r="G6" s="19">
-        <v>2.17</v>
-      </c>
-      <c r="H6" s="19">
+      <c r="G6" s="18">
+        <v>2.15</v>
+      </c>
+      <c r="H6" s="18">
         <v>12.25</v>
       </c>
-      <c r="I6" s="12">
-        <v>5.65</v>
+      <c r="I6" s="8">
+        <v>5.7</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1816,7 +1820,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1833,7 +1837,7 @@
       <c r="H7" s="22">
         <v>2.6</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="21">
         <v>1.53</v>
       </c>
     </row>
@@ -1845,7 +1849,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1862,7 +1866,7 @@
       <c r="H8" s="25">
         <v>1.6</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="21">
         <v>2.4</v>
       </c>
     </row>
@@ -1874,7 +1878,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1891,7 +1895,7 @@
       <c r="H9" s="28">
         <v>5.75</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="21">
         <v>3.67</v>
       </c>
     </row>
@@ -1903,7 +1907,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1920,13 +1924,13 @@
       <c r="H10" s="31">
         <v>0.65</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="21">
         <v>1.34</v>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B11" s="36" t="s">
         <v>30</v>
@@ -1944,13 +1948,13 @@
         <v>-45.1</v>
       </c>
       <c r="G11" s="36">
-        <v>9.13</v>
+        <v>9.12</v>
       </c>
       <c r="H11" s="36">
         <v>41.39</v>
       </c>
       <c r="I11" s="36">
-        <v>4.53</v>
+        <v>4.54</v>
       </c>
     </row>
   </sheetData>
